--- a/Email_finder.xlsx
+++ b/Email_finder.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Shivani\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anujsingh/Documents/automation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563F4E1E-6578-4C4E-AFDC-DDA9973E152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{460B5271-4868-C74F-81D2-D0E4512BAC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26C77154-E709-4964-BA1B-1217154A3DD5}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="23260" windowHeight="12460" xr2:uid="{26C77154-E709-4964-BA1B-1217154A3DD5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
   <si>
     <t>Employee</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>svignesh90@yahoo.co.in</t>
+  </si>
+  <si>
+    <t>sent</t>
   </si>
 </sst>
 </file>
@@ -575,15 +578,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAB4B86F-A047-4604-AA83-416B5A55928C}">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="43.44140625" customWidth="1"/>
-    <col min="2" max="2" width="24.5546875" customWidth="1"/>
+    <col min="1" max="1" width="43.5" customWidth="1"/>
+    <col min="2" max="2" width="24.5" customWidth="1"/>
     <col min="3" max="3" width="35.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -593,8 +596,11 @@
       <c r="C1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" ht="28.8" x14ac:dyDescent="0.45">
+      <c r="D1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -605,7 +611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -616,7 +622,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
@@ -627,7 +633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
@@ -638,7 +644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -649,7 +655,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -660,7 +666,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
@@ -671,7 +677,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
@@ -682,7 +688,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -693,7 +699,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -704,7 +710,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
@@ -715,7 +721,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>23</v>
       </c>
@@ -726,7 +732,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -737,7 +743,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
@@ -748,7 +754,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" ht="21" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>29</v>
       </c>
@@ -759,7 +765,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" ht="21" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>29</v>
       </c>
@@ -770,7 +776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" ht="21" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>30</v>
       </c>
@@ -781,7 +787,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" ht="21" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
@@ -792,7 +798,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" ht="21" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>33</v>
       </c>
@@ -803,7 +809,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" ht="21" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>34</v>
       </c>
@@ -814,7 +820,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" ht="21" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>34</v>
       </c>
@@ -825,7 +831,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" ht="21" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>39</v>
       </c>
@@ -836,7 +842,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" ht="21" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>40</v>
       </c>
@@ -847,7 +853,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="20.399999999999999" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" ht="21" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>40</v>
       </c>
